--- a/results/ai_run/543-2/5_quantification/543-2_quantification.xlsx
+++ b/results/ai_run/543-2/5_quantification/543-2_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12.9167</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5022</v>
+        <v>2.6629</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5.8706</v>
+        <v>4.0113</v>
       </c>
       <c r="D25" t="n">
-        <v>6.3277</v>
+        <v>3.9619</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2856</v>
+        <v>0.6761</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -2592,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M2" t="n">
         <v>514</v>
@@ -2631,7 +2631,7 @@
         <v>0.05871968</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.5442</v>
+        <v>5.3171</v>
       </c>
       <c r="Z2" t="n">
         <v>485</v>
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>614</v>
@@ -2738,7 +2738,7 @@
         <v>0.05683073</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.0827</v>
+        <v>4.0661</v>
       </c>
       <c r="Z3" t="n">
         <v>566</v>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
         <v>386</v>
@@ -2845,7 +2845,7 @@
         <v>0.05148337</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.3623</v>
+        <v>4.6271</v>
       </c>
       <c r="Z4" t="n">
         <v>354</v>
@@ -2913,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M5" t="n">
         <v>382</v>
@@ -2952,7 +2952,7 @@
         <v>0.03751651</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.3001</v>
+        <v>3.8701</v>
       </c>
       <c r="Z5" t="n">
         <v>356</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
         <v>355</v>
@@ -3059,7 +3059,7 @@
         <v>0.05393422</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.7787</v>
+        <v>3.8894</v>
       </c>
       <c r="Z6" t="n">
         <v>276</v>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
         <v>301</v>
@@ -3273,7 +3273,7 @@
         <v>0.04914441</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.4134</v>
+        <v>3.2067</v>
       </c>
       <c r="Z8" t="n">
         <v>251</v>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M9" t="n">
         <v>454</v>
@@ -3380,7 +3380,7 @@
         <v>0.05105396</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.293</v>
+        <v>4.7198</v>
       </c>
       <c r="Z9" t="n">
         <v>437</v>
@@ -3448,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="M10" t="n">
         <v>424</v>
@@ -3487,7 +3487,7 @@
         <v>0.04762274</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.8573</v>
+        <v>3.97</v>
       </c>
       <c r="Z10" t="n">
         <v>348</v>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M11" t="n">
         <v>387</v>
@@ -3594,7 +3594,7 @@
         <v>0.05118395</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.8326</v>
+        <v>3.9539</v>
       </c>
       <c r="Z11" t="n">
         <v>306</v>
@@ -3662,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="M12" t="n">
         <v>435</v>
@@ -3701,7 +3701,7 @@
         <v>0.05151774</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.5381</v>
+        <v>3.1039</v>
       </c>
       <c r="Z12" t="n">
         <v>382</v>
@@ -3769,7 +3769,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
         <v>316</v>
@@ -3808,7 +3808,7 @@
         <v>0.0448838</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.1296</v>
+        <v>3.0972</v>
       </c>
       <c r="Z13" t="n">
         <v>313</v>
